--- a/Data/Pond plant transplanting result-2019/DI.xlsx
+++ b/Data/Pond plant transplanting result-2019/DI.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10609"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995EA1FD-C164-124A-B1F3-464DD23EC344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CD7BF9-8915-CE48-ACAD-3A691AAABF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17980" tabRatio="863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17980" tabRatio="863" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plant growth" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Biomass" sheetId="9" r:id="rId3"/>
     <sheet name="Flowering" sheetId="10" r:id="rId4"/>
     <sheet name="Salinity" sheetId="6" r:id="rId5"/>
+    <sheet name="Survival rate" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Biomass!$B$1:$B$56</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3346" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3404" uniqueCount="150">
   <si>
     <t>ID</t>
   </si>
@@ -523,6 +524,15 @@
   <si>
     <t>Neighbor removal</t>
   </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Survival rate (%)</t>
+  </si>
+  <si>
+    <t>Deal Island</t>
+  </si>
 </sst>
 </file>
 
@@ -531,7 +541,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,6 +611,12 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -23862,4 +23878,285 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BAD1E68-FDA3-564F-8599-A040E96DB051}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8">
+        <v>80</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19">
+        <v>100</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/Pond plant transplanting result-2019/DI.xlsx
+++ b/Data/Pond plant transplanting result-2019/DI.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CD7BF9-8915-CE48-ACAD-3A691AAABF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF35C2C-7716-E246-96E0-8385EDF05CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17980" tabRatio="863" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12780" yWindow="0" windowWidth="30240" windowHeight="17980" tabRatio="863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plant growth" sheetId="1" r:id="rId1"/>
     <sheet name="Redox and Soil strength" sheetId="8" r:id="rId2"/>
-    <sheet name="Biomass" sheetId="9" r:id="rId3"/>
-    <sheet name="Flowering" sheetId="10" r:id="rId4"/>
-    <sheet name="Salinity" sheetId="6" r:id="rId5"/>
-    <sheet name="Survival rate" sheetId="11" r:id="rId6"/>
+    <sheet name="Flowering" sheetId="10" r:id="rId3"/>
+    <sheet name="Salinity" sheetId="6" r:id="rId4"/>
+    <sheet name="Survival rate" sheetId="11" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Biomass!$B$1:$B$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plant growth'!$B$1:$B$441</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3404" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3274" uniqueCount="147">
   <si>
     <t>ID</t>
   </si>
@@ -419,16 +417,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dead biomass (g)</t>
-  </si>
-  <si>
-    <t>Live biomass (g)</t>
-  </si>
-  <si>
-    <t>Note</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Jun-21</t>
   </si>
   <si>
@@ -541,7 +529,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -607,42 +595,18 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E75B5"/>
-        <bgColor rgb="FF2E75B5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE598"/>
-        <bgColor rgb="FFFFE598"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF548135"/>
-        <bgColor rgb="FF548135"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -665,7 +629,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -679,14 +643,9 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -984,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -1013,7 +972,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C2" s="2">
         <v>47</v>
@@ -1043,7 +1002,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C3" s="2">
         <v>37</v>
@@ -1073,7 +1032,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C4" s="2">
         <v>24</v>
@@ -1103,7 +1062,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C5" s="2">
         <v>26</v>
@@ -1133,7 +1092,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C6" s="2">
         <v>43</v>
@@ -1163,7 +1122,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C7" s="2">
         <v>54</v>
@@ -1193,7 +1152,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C8" s="2">
         <v>53</v>
@@ -1223,7 +1182,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2">
         <v>37</v>
@@ -1253,7 +1212,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2">
         <v>21</v>
@@ -1283,7 +1242,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2">
         <v>25</v>
@@ -1313,7 +1272,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2">
         <v>17</v>
@@ -1343,7 +1302,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C13" s="2">
         <v>35</v>
@@ -1373,7 +1332,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C14" s="2">
         <v>13</v>
@@ -1403,7 +1362,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C15" s="2">
         <v>19</v>
@@ -1433,7 +1392,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2">
         <v>45</v>
@@ -1463,7 +1422,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2">
         <v>65</v>
@@ -1493,7 +1452,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2">
         <v>20</v>
@@ -1523,7 +1482,7 @@
         <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2">
         <v>24</v>
@@ -1553,7 +1512,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2">
         <v>19</v>
@@ -1583,7 +1542,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C21" s="2">
         <v>36</v>
@@ -1913,7 +1872,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C32" s="2">
         <v>18</v>
@@ -1943,7 +1902,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C33" s="2">
         <v>26</v>
@@ -1973,7 +1932,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="2">
         <v>23</v>
@@ -2003,7 +1962,7 @@
         <v>41</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C35" s="2">
         <v>40</v>
@@ -2033,7 +1992,7 @@
         <v>42</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C36" s="2">
         <v>42</v>
@@ -2063,7 +2022,7 @@
         <v>43</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C37" s="2">
         <v>38</v>
@@ -2093,7 +2052,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C38" s="2">
         <v>23</v>
@@ -2123,7 +2082,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C39" s="2">
         <v>35</v>
@@ -2153,7 +2112,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="2">
         <v>29</v>
@@ -2183,7 +2142,7 @@
         <v>47</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C41" s="2">
         <v>46</v>
@@ -2213,7 +2172,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C42" s="2">
         <v>31</v>
@@ -2243,7 +2202,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C43" s="2">
         <v>22</v>
@@ -2273,7 +2232,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C44" s="2">
         <v>13</v>
@@ -2303,7 +2262,7 @@
         <v>51</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C45" s="2">
         <v>16</v>
@@ -2333,7 +2292,7 @@
         <v>52</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C46" s="2">
         <v>11</v>
@@ -2363,7 +2322,7 @@
         <v>53</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C47" s="2">
         <v>30</v>
@@ -2393,7 +2352,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C48" s="2">
         <v>20</v>
@@ -2423,7 +2382,7 @@
         <v>55</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C49" s="2">
         <v>23</v>
@@ -2453,7 +2412,7 @@
         <v>56</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C50" s="2">
         <v>49</v>
@@ -2483,7 +2442,7 @@
         <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C51" s="2">
         <v>40</v>
@@ -2663,7 +2622,7 @@
         <v>3</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C57" s="2">
         <v>38</v>
@@ -2693,7 +2652,7 @@
         <v>4</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C58" s="2">
         <v>45</v>
@@ -2723,7 +2682,7 @@
         <v>5</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C59" s="2">
         <v>30</v>
@@ -2753,7 +2712,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C60" s="2">
         <v>24</v>
@@ -2783,7 +2742,7 @@
         <v>7</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C61" s="2">
         <v>38</v>
@@ -2813,7 +2772,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C62" s="2">
         <v>47</v>
@@ -2843,7 +2802,7 @@
         <v>9</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C63" s="2">
         <v>52</v>
@@ -2873,7 +2832,7 @@
         <v>10</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C64" s="2">
         <v>31</v>
@@ -2903,7 +2862,7 @@
         <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C65" s="2">
         <v>23</v>
@@ -2933,7 +2892,7 @@
         <v>12</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C66" s="2">
         <v>21</v>
@@ -2963,7 +2922,7 @@
         <v>13</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C67" s="2">
         <v>16</v>
@@ -2993,7 +2952,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C68" s="2">
         <v>24</v>
@@ -3023,7 +2982,7 @@
         <v>15</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C69" s="2">
         <v>11</v>
@@ -3053,7 +3012,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C70" s="2">
         <v>13</v>
@@ -3083,7 +3042,7 @@
         <v>17</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C71" s="2">
         <v>39</v>
@@ -3113,7 +3072,7 @@
         <v>18</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C72" s="2">
         <v>64</v>
@@ -3143,7 +3102,7 @@
         <v>19</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C73" s="2">
         <v>18</v>
@@ -3173,7 +3132,7 @@
         <v>20</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C74" s="2">
         <v>17</v>
@@ -3203,7 +3162,7 @@
         <v>21</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C75" s="2">
         <v>24</v>
@@ -3233,7 +3192,7 @@
         <v>22</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C76" s="2">
         <v>35</v>
@@ -3563,7 +3522,7 @@
         <v>38</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C87" s="2">
         <v>23</v>
@@ -3593,7 +3552,7 @@
         <v>39</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C88" s="2">
         <v>25</v>
@@ -3623,7 +3582,7 @@
         <v>40</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C89" s="2">
         <v>27</v>
@@ -3653,7 +3612,7 @@
         <v>41</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C90" s="2">
         <v>8</v>
@@ -3683,7 +3642,7 @@
         <v>42</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C91" s="2">
         <v>42</v>
@@ -3713,7 +3672,7 @@
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C92" s="2">
         <v>33</v>
@@ -3743,7 +3702,7 @@
         <v>44</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C93" s="2">
         <v>24</v>
@@ -3773,7 +3732,7 @@
         <v>45</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C94" s="2">
         <v>34</v>
@@ -3803,7 +3762,7 @@
         <v>46</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C95" s="2">
         <v>31</v>
@@ -3833,7 +3792,7 @@
         <v>47</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C96" s="2">
         <v>46</v>
@@ -3863,7 +3822,7 @@
         <v>48</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C97" s="2">
         <v>30</v>
@@ -3893,7 +3852,7 @@
         <v>49</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C98" s="2">
         <v>25</v>
@@ -3923,7 +3882,7 @@
         <v>50</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C99" s="2">
         <v>19</v>
@@ -3953,7 +3912,7 @@
         <v>51</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C100" s="2">
         <v>16</v>
@@ -3983,7 +3942,7 @@
         <v>52</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C101" s="2">
         <v>5</v>
@@ -4013,7 +3972,7 @@
         <v>53</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C102" s="2">
         <v>31</v>
@@ -4043,7 +4002,7 @@
         <v>54</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C103" s="2">
         <v>18</v>
@@ -4073,7 +4032,7 @@
         <v>55</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C104" s="2">
         <v>26</v>
@@ -4103,7 +4062,7 @@
         <v>56</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C105" s="2">
         <v>44</v>
@@ -4133,7 +4092,7 @@
         <v>57</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C106" s="2">
         <v>37</v>
@@ -4313,7 +4272,7 @@
         <v>3</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C112" s="2">
         <v>41</v>
@@ -4343,7 +4302,7 @@
         <v>4</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C113" s="2">
         <v>45</v>
@@ -4373,7 +4332,7 @@
         <v>5</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C114" s="2">
         <v>33</v>
@@ -4403,7 +4362,7 @@
         <v>6</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C115" s="2">
         <v>23</v>
@@ -4433,7 +4392,7 @@
         <v>7</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C116" s="2">
         <v>47</v>
@@ -4463,7 +4422,7 @@
         <v>8</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C117" s="2">
         <v>47</v>
@@ -4493,7 +4452,7 @@
         <v>9</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C118" s="2">
         <v>52</v>
@@ -4523,7 +4482,7 @@
         <v>10</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C119" s="2">
         <v>30</v>
@@ -4553,7 +4512,7 @@
         <v>11</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C120" s="2">
         <v>22</v>
@@ -4583,7 +4542,7 @@
         <v>12</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C121" s="2">
         <v>25</v>
@@ -4613,7 +4572,7 @@
         <v>13</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C122" s="2">
         <v>18</v>
@@ -4643,7 +4602,7 @@
         <v>14</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C123" s="2">
         <v>21</v>
@@ -4673,7 +4632,7 @@
         <v>15</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C124" s="2">
         <v>13</v>
@@ -4703,7 +4662,7 @@
         <v>16</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C125" s="2">
         <v>11</v>
@@ -4733,7 +4692,7 @@
         <v>17</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C126" s="2">
         <v>41</v>
@@ -4763,7 +4722,7 @@
         <v>18</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C127" s="2">
         <v>53</v>
@@ -4793,7 +4752,7 @@
         <v>19</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C128" s="2">
         <v>22</v>
@@ -4823,7 +4782,7 @@
         <v>20</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C129" s="2">
         <v>16</v>
@@ -4853,7 +4812,7 @@
         <v>21</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C130" s="2">
         <v>19</v>
@@ -4883,7 +4842,7 @@
         <v>22</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C131" s="2">
         <v>28</v>
@@ -5213,7 +5172,7 @@
         <v>38</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C142" s="2">
         <v>26</v>
@@ -5243,7 +5202,7 @@
         <v>39</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C143" s="2">
         <v>27</v>
@@ -5273,7 +5232,7 @@
         <v>40</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C144" s="2">
         <v>30</v>
@@ -5303,7 +5262,7 @@
         <v>41</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C145" s="2">
         <v>8</v>
@@ -5333,7 +5292,7 @@
         <v>42</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C146" s="2">
         <v>43</v>
@@ -5363,7 +5322,7 @@
         <v>43</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C147" s="2">
         <v>34</v>
@@ -5393,7 +5352,7 @@
         <v>44</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C148" s="2">
         <v>26</v>
@@ -5423,7 +5382,7 @@
         <v>45</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C149" s="2">
         <v>39</v>
@@ -5453,7 +5412,7 @@
         <v>46</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C150" s="2">
         <v>32</v>
@@ -5483,7 +5442,7 @@
         <v>47</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C151" s="2">
         <v>38</v>
@@ -5513,7 +5472,7 @@
         <v>48</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C152" s="2">
         <v>27</v>
@@ -5543,7 +5502,7 @@
         <v>49</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C153" s="2">
         <v>24</v>
@@ -5573,7 +5532,7 @@
         <v>50</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C154" s="2">
         <v>20</v>
@@ -5603,7 +5562,7 @@
         <v>51</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C155" s="2">
         <v>17</v>
@@ -5633,7 +5592,7 @@
         <v>52</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C156" s="6">
         <v>4</v>
@@ -5653,7 +5612,7 @@
       <c r="H156" s="6">
         <v>0</v>
       </c>
-      <c r="I156" s="19" t="s">
+      <c r="I156" s="15" t="s">
         <v>102</v>
       </c>
       <c r="J156" s="6"/>
@@ -5665,7 +5624,7 @@
         <v>53</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C157" s="2">
         <v>31</v>
@@ -5695,7 +5654,7 @@
         <v>54</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C158" s="2">
         <v>21</v>
@@ -5725,7 +5684,7 @@
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C159" s="2">
         <v>22</v>
@@ -5755,7 +5714,7 @@
         <v>56</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C160" s="2">
         <v>44</v>
@@ -5785,7 +5744,7 @@
         <v>57</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C161" s="2">
         <v>36</v>
@@ -5965,7 +5924,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C167" s="2">
         <v>48</v>
@@ -5995,7 +5954,7 @@
         <v>4</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C168" s="2">
         <v>52</v>
@@ -6025,7 +5984,7 @@
         <v>5</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C169" s="2">
         <v>34</v>
@@ -6055,7 +6014,7 @@
         <v>6</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C170" s="2">
         <v>22</v>
@@ -6085,7 +6044,7 @@
         <v>7</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C171" s="2">
         <v>48</v>
@@ -6115,7 +6074,7 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C172" s="2">
         <v>32</v>
@@ -6145,7 +6104,7 @@
         <v>9</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C173" s="2">
         <v>50</v>
@@ -6175,7 +6134,7 @@
         <v>10</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C174" s="2">
         <v>14</v>
@@ -6205,7 +6164,7 @@
         <v>11</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C175" s="2">
         <v>18</v>
@@ -6235,7 +6194,7 @@
         <v>12</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C176" s="2">
         <v>13</v>
@@ -6265,7 +6224,7 @@
         <v>13</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C177" s="2">
         <v>21</v>
@@ -6295,7 +6254,7 @@
         <v>14</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C178" s="2">
         <v>16</v>
@@ -6325,7 +6284,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C179" s="2">
         <v>13</v>
@@ -6355,7 +6314,7 @@
         <v>16</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C180" s="6">
         <v>4</v>
@@ -6375,7 +6334,7 @@
       <c r="H180" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I180" s="19" t="s">
+      <c r="I180" s="15" t="s">
         <v>105</v>
       </c>
       <c r="J180" s="6"/>
@@ -6387,7 +6346,7 @@
         <v>17</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C181" s="2">
         <v>39</v>
@@ -6417,7 +6376,7 @@
         <v>18</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C182" s="2">
         <v>38</v>
@@ -6447,7 +6406,7 @@
         <v>19</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C183" s="2">
         <v>25</v>
@@ -6477,7 +6436,7 @@
         <v>20</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C184" s="2">
         <v>14</v>
@@ -6507,7 +6466,7 @@
         <v>21</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C185" s="2">
         <v>20</v>
@@ -6537,7 +6496,7 @@
         <v>22</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C186" s="2">
         <v>20</v>
@@ -6868,7 +6827,7 @@
         <v>38</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C197" s="2">
         <v>23</v>
@@ -6898,7 +6857,7 @@
         <v>39</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C198" s="2">
         <v>30</v>
@@ -6928,7 +6887,7 @@
         <v>40</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C199" s="2">
         <v>24</v>
@@ -6958,7 +6917,7 @@
         <v>41</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C200" s="6">
         <v>4</v>
@@ -6978,7 +6937,7 @@
       <c r="H200" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I200" s="19" t="s">
+      <c r="I200" s="15" t="s">
         <v>105</v>
       </c>
       <c r="J200" s="6"/>
@@ -6990,7 +6949,7 @@
         <v>42</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C201" s="2">
         <v>43</v>
@@ -7020,7 +6979,7 @@
         <v>43</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C202" s="2">
         <v>34</v>
@@ -7050,7 +7009,7 @@
         <v>44</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C203" s="2">
         <v>31</v>
@@ -7080,7 +7039,7 @@
         <v>45</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C204" s="2">
         <v>40</v>
@@ -7110,7 +7069,7 @@
         <v>46</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C205" s="2">
         <v>30</v>
@@ -7140,7 +7099,7 @@
         <v>47</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C206" s="2">
         <v>35</v>
@@ -7170,7 +7129,7 @@
         <v>48</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C207" s="2">
         <v>28</v>
@@ -7200,7 +7159,7 @@
         <v>49</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C208" s="2">
         <v>22</v>
@@ -7230,7 +7189,7 @@
         <v>50</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C209" s="2">
         <v>16</v>
@@ -7260,7 +7219,7 @@
         <v>51</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C210" s="2">
         <v>16</v>
@@ -7290,7 +7249,7 @@
         <v>52</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C211" s="2">
         <v>4</v>
@@ -7320,7 +7279,7 @@
         <v>53</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C212" s="2">
         <v>33</v>
@@ -7350,7 +7309,7 @@
         <v>54</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C213" s="2">
         <v>20</v>
@@ -7380,7 +7339,7 @@
         <v>55</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C214" s="2">
         <v>15</v>
@@ -7410,7 +7369,7 @@
         <v>56</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C215" s="2">
         <v>41</v>
@@ -7440,7 +7399,7 @@
         <v>57</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C216" s="2">
         <v>39</v>
@@ -7620,7 +7579,7 @@
         <v>3</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C222" s="2">
         <v>61</v>
@@ -7650,7 +7609,7 @@
         <v>4</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C223" s="2">
         <v>55</v>
@@ -7680,7 +7639,7 @@
         <v>5</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C224" s="2">
         <v>38</v>
@@ -7710,7 +7669,7 @@
         <v>6</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C225" s="2">
         <v>15</v>
@@ -7740,7 +7699,7 @@
         <v>7</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C226" s="2">
         <v>57</v>
@@ -7770,7 +7729,7 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C227" s="2">
         <v>39</v>
@@ -7800,7 +7759,7 @@
         <v>9</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C228" s="2">
         <v>57</v>
@@ -7830,7 +7789,7 @@
         <v>10</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C229" s="2">
         <v>11</v>
@@ -7860,7 +7819,7 @@
         <v>11</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C230" s="2">
         <v>18</v>
@@ -7890,7 +7849,7 @@
         <v>12</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C231" s="2">
         <v>3</v>
@@ -7920,7 +7879,7 @@
         <v>13</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C232" s="2">
         <v>26</v>
@@ -7950,7 +7909,7 @@
         <v>14</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C233" s="2">
         <v>12</v>
@@ -7980,7 +7939,7 @@
         <v>15</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C234" s="2">
         <v>16</v>
@@ -8010,7 +7969,7 @@
         <v>16</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
@@ -8043,7 +8002,7 @@
         <v>17</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C236" s="2">
         <v>46</v>
@@ -8073,7 +8032,7 @@
         <v>18</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C237" s="2">
         <v>46</v>
@@ -8103,7 +8062,7 @@
         <v>19</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C238" s="2">
         <v>25</v>
@@ -8133,7 +8092,7 @@
         <v>20</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C239" s="2">
         <v>4</v>
@@ -8163,7 +8122,7 @@
         <v>21</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C240" s="2">
         <v>27</v>
@@ -8193,7 +8152,7 @@
         <v>22</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C241" s="2">
         <v>22</v>
@@ -8523,7 +8482,7 @@
         <v>38</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C252" s="2">
         <v>20</v>
@@ -8553,7 +8512,7 @@
         <v>39</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C253" s="2">
         <v>20</v>
@@ -8583,7 +8542,7 @@
         <v>40</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C254" s="2">
         <v>21</v>
@@ -8613,7 +8572,7 @@
         <v>41</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C255" s="2">
         <v>3</v>
@@ -8643,7 +8602,7 @@
         <v>42</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C256" s="2">
         <v>36</v>
@@ -8673,7 +8632,7 @@
         <v>43</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C257" s="2">
         <v>30</v>
@@ -8703,7 +8662,7 @@
         <v>44</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C258" s="2">
         <v>34</v>
@@ -8733,7 +8692,7 @@
         <v>45</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C259" s="2">
         <v>46</v>
@@ -8763,7 +8722,7 @@
         <v>46</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C260" s="2">
         <v>25</v>
@@ -8793,7 +8752,7 @@
         <v>47</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C261" s="2">
         <v>40</v>
@@ -8823,7 +8782,7 @@
         <v>48</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C262" s="2">
         <v>32</v>
@@ -8853,7 +8812,7 @@
         <v>49</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C263" s="2">
         <v>23</v>
@@ -8883,7 +8842,7 @@
         <v>50</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C264" s="2">
         <v>11</v>
@@ -8913,7 +8872,7 @@
         <v>51</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C265" s="2">
         <v>17</v>
@@ -8943,7 +8902,7 @@
         <v>52</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C266" s="2">
         <v>3</v>
@@ -8973,7 +8932,7 @@
         <v>53</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C267" s="2">
         <v>31</v>
@@ -9003,7 +8962,7 @@
         <v>54</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C268" s="2">
         <v>16</v>
@@ -9033,7 +8992,7 @@
         <v>55</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C269" s="2">
         <v>15</v>
@@ -9063,7 +9022,7 @@
         <v>56</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C270" s="2">
         <v>40</v>
@@ -9093,7 +9052,7 @@
         <v>57</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C271" s="2">
         <v>37</v>
@@ -9273,7 +9232,7 @@
         <v>3</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C277" s="2">
         <v>97</v>
@@ -9303,7 +9262,7 @@
         <v>4</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C278" s="2">
         <v>84</v>
@@ -9333,7 +9292,7 @@
         <v>5</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C279" s="2">
         <v>47</v>
@@ -9363,7 +9322,7 @@
         <v>6</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C280" s="2">
         <v>4</v>
@@ -9390,7 +9349,7 @@
         <v>7</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C281" s="2">
         <v>68</v>
@@ -9420,7 +9379,7 @@
         <v>8</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C282" s="2">
         <v>0</v>
@@ -9453,7 +9412,7 @@
         <v>9</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C283" s="2">
         <v>73</v>
@@ -9483,7 +9442,7 @@
         <v>10</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C284" s="2">
         <v>8</v>
@@ -9516,7 +9475,7 @@
         <v>11</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C285" s="2">
         <v>47</v>
@@ -9546,7 +9505,7 @@
         <v>12</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C286" s="2">
         <v>5</v>
@@ -9576,7 +9535,7 @@
         <v>13</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C287" s="2">
         <v>46</v>
@@ -9606,7 +9565,7 @@
         <v>14</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C288" s="2">
         <v>13</v>
@@ -9636,7 +9595,7 @@
         <v>15</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C289" s="2">
         <v>41</v>
@@ -9666,7 +9625,7 @@
         <v>16</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C290" s="6">
         <v>0</v>
@@ -9705,7 +9664,7 @@
         <v>17</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C291" s="2">
         <v>60</v>
@@ -9735,7 +9694,7 @@
         <v>18</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C292" s="2">
         <v>47</v>
@@ -9765,7 +9724,7 @@
         <v>19</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C293" s="2">
         <v>35</v>
@@ -9795,7 +9754,7 @@
         <v>20</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C294" s="2">
         <v>5</v>
@@ -9825,7 +9784,7 @@
         <v>21</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C295" s="2">
         <v>45</v>
@@ -9855,7 +9814,7 @@
         <v>22</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C296" s="2">
         <v>15</v>
@@ -10185,7 +10144,7 @@
         <v>38</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C307" s="2">
         <v>37</v>
@@ -10215,7 +10174,7 @@
         <v>39</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C308" s="2">
         <v>44</v>
@@ -10245,7 +10204,7 @@
         <v>40</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C309" s="2">
         <v>26</v>
@@ -10275,7 +10234,7 @@
         <v>41</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C310" s="6">
         <v>1</v>
@@ -10314,7 +10273,7 @@
         <v>42</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C311" s="2">
         <v>68</v>
@@ -10344,7 +10303,7 @@
         <v>43</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C312" s="2">
         <v>39</v>
@@ -10374,7 +10333,7 @@
         <v>44</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C313" s="2">
         <v>71</v>
@@ -10404,7 +10363,7 @@
         <v>45</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C314" s="2">
         <v>73</v>
@@ -10434,7 +10393,7 @@
         <v>46</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C315" s="2">
         <v>49</v>
@@ -10464,7 +10423,7 @@
         <v>47</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C316" s="2">
         <v>69</v>
@@ -10494,7 +10453,7 @@
         <v>48</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C317" s="2">
         <v>31</v>
@@ -10527,7 +10486,7 @@
         <v>49</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C318" s="2">
         <v>32</v>
@@ -10557,7 +10516,7 @@
         <v>50</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C319" s="2">
         <v>21</v>
@@ -10587,7 +10546,7 @@
         <v>51</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C320" s="2">
         <v>22</v>
@@ -10617,7 +10576,7 @@
         <v>52</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C321" s="2">
         <v>10</v>
@@ -10654,7 +10613,7 @@
         <v>53</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C322" s="2">
         <v>59</v>
@@ -10684,7 +10643,7 @@
         <v>54</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C323" s="2">
         <v>41</v>
@@ -10714,7 +10673,7 @@
         <v>55</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C324" s="2">
         <v>25</v>
@@ -10744,7 +10703,7 @@
         <v>56</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C325" s="2">
         <v>54</v>
@@ -10774,7 +10733,7 @@
         <v>57</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C326" s="2">
         <v>15</v>
@@ -10954,7 +10913,7 @@
         <v>3</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C332" s="11">
         <v>90</v>
@@ -10975,7 +10934,7 @@
         <v>70</v>
       </c>
       <c r="I332" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J332" s="11"/>
       <c r="K332" s="11"/>
@@ -10986,7 +10945,7 @@
         <v>4</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C333" s="11">
         <v>48</v>
@@ -11007,7 +10966,7 @@
         <v>69</v>
       </c>
       <c r="I333" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J333" s="11"/>
       <c r="K333" s="11"/>
@@ -11018,7 +10977,7 @@
         <v>5</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C334" s="11">
         <v>41</v>
@@ -11039,7 +10998,7 @@
         <v>69</v>
       </c>
       <c r="I334" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J334" s="11"/>
       <c r="K334" s="11"/>
@@ -11050,7 +11009,7 @@
         <v>6</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C335" s="11">
         <v>0</v>
@@ -11071,7 +11030,7 @@
         <v>0</v>
       </c>
       <c r="I335" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J335" s="11"/>
       <c r="K335" s="11" t="s">
@@ -11084,7 +11043,7 @@
         <v>7</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C336" s="11">
         <v>66</v>
@@ -11105,7 +11064,7 @@
         <v>68</v>
       </c>
       <c r="I336" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J336" s="11"/>
       <c r="K336" s="11"/>
@@ -11116,7 +11075,7 @@
         <v>8</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C337" s="11">
         <v>0</v>
@@ -11137,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="I337" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J337" s="11"/>
       <c r="K337" s="11" t="s">
@@ -11150,7 +11109,7 @@
         <v>9</v>
       </c>
       <c r="B338" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C338" s="11">
         <v>67</v>
@@ -11171,7 +11130,7 @@
         <v>69</v>
       </c>
       <c r="I338" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J338" s="11"/>
       <c r="K338" s="11"/>
@@ -11182,7 +11141,7 @@
         <v>10</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C339" s="11">
         <v>1</v>
@@ -11203,7 +11162,7 @@
         <v>91</v>
       </c>
       <c r="I339" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J339" s="11"/>
       <c r="K339" s="11"/>
@@ -11214,7 +11173,7 @@
         <v>11</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C340" s="11">
         <v>40</v>
@@ -11235,7 +11194,7 @@
         <v>61</v>
       </c>
       <c r="I340" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J340" s="11">
         <v>12</v>
@@ -11248,7 +11207,7 @@
         <v>12</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C341" s="11">
         <v>1</v>
@@ -11269,7 +11228,7 @@
         <v>91</v>
       </c>
       <c r="I341" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J341" s="11"/>
       <c r="K341" s="11"/>
@@ -11280,7 +11239,7 @@
         <v>13</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C342" s="11">
         <v>25</v>
@@ -11301,7 +11260,7 @@
         <v>65</v>
       </c>
       <c r="I342" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J342" s="11"/>
       <c r="K342" s="11"/>
@@ -11312,7 +11271,7 @@
         <v>14</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C343" s="11">
         <v>2</v>
@@ -11333,7 +11292,7 @@
         <v>91</v>
       </c>
       <c r="I343" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J343" s="11"/>
       <c r="K343" s="11"/>
@@ -11344,7 +11303,7 @@
         <v>15</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C344" s="11">
         <v>46</v>
@@ -11365,7 +11324,7 @@
         <v>72</v>
       </c>
       <c r="I344" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J344" s="11"/>
       <c r="K344" s="11"/>
@@ -11376,7 +11335,7 @@
         <v>16</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C345" s="11">
         <v>0</v>
@@ -11397,7 +11356,7 @@
         <v>0</v>
       </c>
       <c r="I345" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J345" s="11"/>
       <c r="K345" s="11" t="s">
@@ -11410,7 +11369,7 @@
         <v>17</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C346" s="11">
         <v>61</v>
@@ -11431,7 +11390,7 @@
         <v>76</v>
       </c>
       <c r="I346" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J346" s="11">
         <v>13</v>
@@ -11444,7 +11403,7 @@
         <v>18</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C347" s="11">
         <v>41</v>
@@ -11465,7 +11424,7 @@
         <v>68</v>
       </c>
       <c r="I347" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J347" s="11"/>
       <c r="K347" s="11"/>
@@ -11476,7 +11435,7 @@
         <v>19</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C348" s="11">
         <v>26</v>
@@ -11497,7 +11456,7 @@
         <v>50</v>
       </c>
       <c r="I348" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J348" s="11"/>
       <c r="K348" s="11"/>
@@ -11508,7 +11467,7 @@
         <v>20</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C349" s="11">
         <v>1</v>
@@ -11529,7 +11488,7 @@
         <v>91</v>
       </c>
       <c r="I349" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J349" s="11"/>
       <c r="K349" s="11"/>
@@ -11540,7 +11499,7 @@
         <v>21</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C350" s="11">
         <v>48</v>
@@ -11561,7 +11520,7 @@
         <v>69</v>
       </c>
       <c r="I350" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J350" s="11"/>
       <c r="K350" s="11"/>
@@ -11572,7 +11531,7 @@
         <v>22</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C351" s="11">
         <v>0</v>
@@ -11593,7 +11552,7 @@
         <v>0</v>
       </c>
       <c r="I351" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J351" s="11"/>
       <c r="K351" s="11" t="s">
@@ -11627,7 +11586,7 @@
         <v>54</v>
       </c>
       <c r="I352" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J352" s="11">
         <v>11</v>
@@ -11661,7 +11620,7 @@
         <v>62</v>
       </c>
       <c r="I353" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J353" s="11"/>
       <c r="K353" s="11"/>
@@ -11693,7 +11652,7 @@
         <v>48</v>
       </c>
       <c r="I354" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J354" s="11"/>
       <c r="K354" s="11"/>
@@ -11725,7 +11684,7 @@
         <v>63</v>
       </c>
       <c r="I355" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J355" s="12"/>
       <c r="K355" s="11"/>
@@ -11757,7 +11716,7 @@
         <v>39</v>
       </c>
       <c r="I356" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J356" s="11"/>
       <c r="K356" s="11"/>
@@ -11789,7 +11748,7 @@
         <v>62</v>
       </c>
       <c r="I357" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J357" s="11"/>
       <c r="K357" s="11"/>
@@ -11821,7 +11780,7 @@
         <v>55</v>
       </c>
       <c r="I358" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J358" s="11">
         <v>11</v>
@@ -11855,7 +11814,7 @@
         <v>55</v>
       </c>
       <c r="I359" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J359" s="11"/>
       <c r="K359" s="11"/>
@@ -11887,7 +11846,7 @@
         <v>49</v>
       </c>
       <c r="I360" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J360" s="11"/>
       <c r="K360" s="11"/>
@@ -11919,7 +11878,7 @@
         <v>64</v>
       </c>
       <c r="I361" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J361" s="11"/>
       <c r="K361" s="11"/>
@@ -11930,7 +11889,7 @@
         <v>38</v>
       </c>
       <c r="B362" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C362" s="11">
         <v>26</v>
@@ -11951,7 +11910,7 @@
         <v>71</v>
       </c>
       <c r="I362" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J362" s="11"/>
       <c r="K362" s="11"/>
@@ -11962,7 +11921,7 @@
         <v>39</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C363" s="11">
         <v>52</v>
@@ -11983,7 +11942,7 @@
         <v>92</v>
       </c>
       <c r="I363" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J363" s="11"/>
       <c r="K363" s="11"/>
@@ -11994,7 +11953,7 @@
         <v>40</v>
       </c>
       <c r="B364" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C364" s="11">
         <v>22</v>
@@ -12015,7 +11974,7 @@
         <v>80</v>
       </c>
       <c r="I364" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J364" s="11"/>
       <c r="K364" s="11"/>
@@ -12026,7 +11985,7 @@
         <v>41</v>
       </c>
       <c r="B365" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C365" s="11">
         <v>2</v>
@@ -12047,7 +12006,7 @@
         <v>91</v>
       </c>
       <c r="I365" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J365" s="11"/>
       <c r="K365" s="11"/>
@@ -12058,7 +12017,7 @@
         <v>42</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C366" s="11">
         <v>48</v>
@@ -12079,7 +12038,7 @@
         <v>74</v>
       </c>
       <c r="I366" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J366" s="11"/>
       <c r="K366" s="11"/>
@@ -12090,7 +12049,7 @@
         <v>43</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C367" s="11">
         <v>33</v>
@@ -12111,7 +12070,7 @@
         <v>85</v>
       </c>
       <c r="I367" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J367" s="11">
         <v>16</v>
@@ -12124,7 +12083,7 @@
         <v>44</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C368" s="11">
         <v>67</v>
@@ -12145,7 +12104,7 @@
         <v>70</v>
       </c>
       <c r="I368" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J368" s="11"/>
       <c r="K368" s="11"/>
@@ -12156,7 +12115,7 @@
         <v>45</v>
       </c>
       <c r="B369" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C369" s="11">
         <v>70</v>
@@ -12177,7 +12136,7 @@
         <v>69.5</v>
       </c>
       <c r="I369" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J369" s="11"/>
       <c r="K369" s="11"/>
@@ -12188,7 +12147,7 @@
         <v>46</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C370" s="11">
         <v>38</v>
@@ -12209,7 +12168,7 @@
         <v>74</v>
       </c>
       <c r="I370" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J370" s="11"/>
       <c r="K370" s="11"/>
@@ -12220,7 +12179,7 @@
         <v>47</v>
       </c>
       <c r="B371" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C371" s="11">
         <v>33</v>
@@ -12241,7 +12200,7 @@
         <v>79</v>
       </c>
       <c r="I371" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J371" s="11"/>
       <c r="K371" s="11"/>
@@ -12252,7 +12211,7 @@
         <v>48</v>
       </c>
       <c r="B372" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C372" s="11">
         <v>26</v>
@@ -12273,7 +12232,7 @@
         <v>61</v>
       </c>
       <c r="I372" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J372" s="11"/>
       <c r="K372" s="11"/>
@@ -12284,7 +12243,7 @@
         <v>49</v>
       </c>
       <c r="B373" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C373" s="11">
         <v>25</v>
@@ -12305,11 +12264,11 @@
         <v>55</v>
       </c>
       <c r="I373" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J373" s="11"/>
       <c r="K373" s="12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q373" s="5"/>
     </row>
@@ -12318,7 +12277,7 @@
         <v>50</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C374" s="11">
         <v>13</v>
@@ -12339,7 +12298,7 @@
         <v>49</v>
       </c>
       <c r="I374" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J374" s="11">
         <v>15</v>
@@ -12352,7 +12311,7 @@
         <v>51</v>
       </c>
       <c r="B375" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C375" s="11">
         <v>17</v>
@@ -12373,7 +12332,7 @@
         <v>62</v>
       </c>
       <c r="I375" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J375" s="11"/>
       <c r="K375" s="11"/>
@@ -12384,7 +12343,7 @@
         <v>52</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C376" s="11">
         <v>11</v>
@@ -12405,7 +12364,7 @@
         <v>42</v>
       </c>
       <c r="I376" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J376" s="11"/>
       <c r="K376" s="11"/>
@@ -12416,7 +12375,7 @@
         <v>53</v>
       </c>
       <c r="B377" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C377" s="11">
         <v>39</v>
@@ -12437,7 +12396,7 @@
         <v>72</v>
       </c>
       <c r="I377" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J377" s="11"/>
       <c r="K377" s="11"/>
@@ -12448,7 +12407,7 @@
         <v>54</v>
       </c>
       <c r="B378" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C378" s="11">
         <v>34</v>
@@ -12469,7 +12428,7 @@
         <v>63</v>
       </c>
       <c r="I378" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J378" s="11"/>
       <c r="K378" s="11"/>
@@ -12480,7 +12439,7 @@
         <v>55</v>
       </c>
       <c r="B379" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C379" s="11">
         <v>18</v>
@@ -12501,7 +12460,7 @@
         <v>62</v>
       </c>
       <c r="I379" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J379" s="11"/>
       <c r="K379" s="11"/>
@@ -12512,7 +12471,7 @@
         <v>56</v>
       </c>
       <c r="B380" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C380" s="11">
         <v>31</v>
@@ -12533,7 +12492,7 @@
         <v>72</v>
       </c>
       <c r="I380" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J380" s="11"/>
       <c r="K380" s="11"/>
@@ -12544,7 +12503,7 @@
         <v>57</v>
       </c>
       <c r="B381" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C381" s="11">
         <v>15</v>
@@ -12565,7 +12524,7 @@
         <v>53</v>
       </c>
       <c r="I381" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J381" s="11"/>
       <c r="K381" s="11"/>
@@ -12597,7 +12556,7 @@
         <v>92</v>
       </c>
       <c r="I382" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J382" s="11">
         <v>14</v>
@@ -12631,7 +12590,7 @@
         <v>91</v>
       </c>
       <c r="I383" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J383" s="11"/>
       <c r="K383" s="11"/>
@@ -12663,7 +12622,7 @@
         <v>93</v>
       </c>
       <c r="I384" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J384" s="11"/>
       <c r="K384" s="11"/>
@@ -12695,7 +12654,7 @@
         <v>73</v>
       </c>
       <c r="I385" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J385" s="11"/>
       <c r="K385" s="11"/>
@@ -12727,7 +12686,7 @@
         <v>90</v>
       </c>
       <c r="I386" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J386" s="11">
         <v>15</v>
@@ -12740,7 +12699,7 @@
         <v>3</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C387" s="2">
         <v>135</v>
@@ -12761,7 +12720,7 @@
         <v>57</v>
       </c>
       <c r="I387" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q387" s="5"/>
     </row>
@@ -12770,7 +12729,7 @@
         <v>4</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C388" s="2">
         <v>91</v>
@@ -12791,7 +12750,7 @@
         <v>62</v>
       </c>
       <c r="I388" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q388" s="5"/>
     </row>
@@ -12800,7 +12759,7 @@
         <v>5</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C389" s="2">
         <v>76</v>
@@ -12821,7 +12780,7 @@
         <v>52</v>
       </c>
       <c r="I389" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q389" s="5"/>
     </row>
@@ -12830,7 +12789,7 @@
         <v>6</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C390" s="2">
         <v>0</v>
@@ -12851,10 +12810,10 @@
         <v>0</v>
       </c>
       <c r="I390" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K390" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q390" s="5"/>
     </row>
@@ -12863,7 +12822,7 @@
         <v>7</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C391" s="2">
         <v>95</v>
@@ -12884,7 +12843,7 @@
         <v>52</v>
       </c>
       <c r="I391" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q391" s="5"/>
     </row>
@@ -12893,7 +12852,7 @@
         <v>8</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C392" s="2">
         <v>0</v>
@@ -12914,10 +12873,10 @@
         <v>0</v>
       </c>
       <c r="I392" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K392" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q392" s="5"/>
     </row>
@@ -12926,7 +12885,7 @@
         <v>9</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C393" s="2">
         <v>136</v>
@@ -12947,7 +12906,7 @@
         <v>89</v>
       </c>
       <c r="I393" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q393" s="5"/>
     </row>
@@ -12956,7 +12915,7 @@
         <v>10</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C394" s="2">
         <v>0</v>
@@ -12977,10 +12936,10 @@
         <v>0</v>
       </c>
       <c r="I394" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K394" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q394" s="5"/>
     </row>
@@ -12989,7 +12948,7 @@
         <v>11</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C395" s="2">
         <v>113</v>
@@ -13010,7 +12969,7 @@
         <v>58</v>
       </c>
       <c r="I395" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q395" s="5"/>
     </row>
@@ -13019,7 +12978,7 @@
         <v>12</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C396" s="2">
         <v>0</v>
@@ -13040,10 +12999,10 @@
         <v>0</v>
       </c>
       <c r="I396" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K396" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q396" s="5"/>
     </row>
@@ -13052,7 +13011,7 @@
         <v>13</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C397" s="2">
         <v>89</v>
@@ -13073,7 +13032,7 @@
         <v>68</v>
       </c>
       <c r="I397" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q397" s="5"/>
     </row>
@@ -13082,7 +13041,7 @@
         <v>14</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C398" s="2">
         <v>0</v>
@@ -13103,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="I398" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K398" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q398" s="5"/>
     </row>
@@ -13115,7 +13074,7 @@
         <v>15</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C399" s="2">
         <v>64</v>
@@ -13136,7 +13095,7 @@
         <v>50</v>
       </c>
       <c r="I399" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q399" s="5"/>
     </row>
@@ -13145,7 +13104,7 @@
         <v>16</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C400" s="2">
         <v>0</v>
@@ -13166,10 +13125,10 @@
         <v>0</v>
       </c>
       <c r="I400" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K400" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q400" s="5"/>
     </row>
@@ -13178,7 +13137,7 @@
         <v>17</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C401" s="2">
         <v>79</v>
@@ -13199,7 +13158,7 @@
         <v>49</v>
       </c>
       <c r="I401" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q401" s="5"/>
     </row>
@@ -13208,7 +13167,7 @@
         <v>18</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C402" s="2">
         <v>0</v>
@@ -13229,10 +13188,10 @@
         <v>0</v>
       </c>
       <c r="I402" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K402" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q402" s="5"/>
     </row>
@@ -13241,7 +13200,7 @@
         <v>19</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C403" s="2">
         <v>38</v>
@@ -13262,7 +13221,7 @@
         <v>56</v>
       </c>
       <c r="I403" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q403" s="5"/>
     </row>
@@ -13271,7 +13230,7 @@
         <v>20</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C404" s="2">
         <v>0</v>
@@ -13292,10 +13251,10 @@
         <v>0</v>
       </c>
       <c r="I404" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K404" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q404" s="5"/>
     </row>
@@ -13304,7 +13263,7 @@
         <v>21</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>115</v>
@@ -13325,10 +13284,10 @@
         <v>115</v>
       </c>
       <c r="I405" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K405" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q405" s="5"/>
     </row>
@@ -13337,7 +13296,7 @@
         <v>22</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C406" s="2">
         <v>0</v>
@@ -13358,10 +13317,10 @@
         <v>0</v>
       </c>
       <c r="I406" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K406" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q406" s="5"/>
     </row>
@@ -13391,7 +13350,7 @@
         <v>52</v>
       </c>
       <c r="I407" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q407" s="5"/>
     </row>
@@ -13421,7 +13380,7 @@
         <v>55</v>
       </c>
       <c r="I408" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q408" s="5"/>
     </row>
@@ -13451,7 +13410,7 @@
         <v>57</v>
       </c>
       <c r="I409" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q409" s="5"/>
     </row>
@@ -13481,7 +13440,7 @@
         <v>62</v>
       </c>
       <c r="I410" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q410" s="5"/>
     </row>
@@ -13511,7 +13470,7 @@
         <v>43</v>
       </c>
       <c r="I411" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q411" s="5"/>
     </row>
@@ -13541,7 +13500,7 @@
         <v>57</v>
       </c>
       <c r="I412" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q412" s="5"/>
     </row>
@@ -13571,7 +13530,7 @@
         <v>50</v>
       </c>
       <c r="I413" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q413" s="5"/>
     </row>
@@ -13601,7 +13560,7 @@
         <v>48</v>
       </c>
       <c r="I414" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q414" s="5"/>
     </row>
@@ -13631,7 +13590,7 @@
         <v>51</v>
       </c>
       <c r="I415" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q415" s="5"/>
     </row>
@@ -13661,7 +13620,7 @@
         <v>54</v>
       </c>
       <c r="I416" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q416" s="5"/>
     </row>
@@ -13670,7 +13629,7 @@
         <v>38</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C417" s="2">
         <v>46</v>
@@ -13691,10 +13650,10 @@
         <v>99</v>
       </c>
       <c r="I417" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K417" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q417" s="5"/>
     </row>
@@ -13703,7 +13662,7 @@
         <v>39</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C418" s="2">
         <v>101</v>
@@ -13724,10 +13683,10 @@
         <v>67</v>
       </c>
       <c r="I418" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K418" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q418" s="5"/>
     </row>
@@ -13736,7 +13695,7 @@
         <v>40</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C419" s="2">
         <v>48</v>
@@ -13757,10 +13716,10 @@
         <v>68</v>
       </c>
       <c r="I419" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K419" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q419" s="5"/>
     </row>
@@ -13769,7 +13728,7 @@
         <v>41</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C420" s="2">
         <v>44</v>
@@ -13790,10 +13749,10 @@
         <v>76</v>
       </c>
       <c r="I420" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K420" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q420" s="5"/>
     </row>
@@ -13802,7 +13761,7 @@
         <v>42</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C421" s="2">
         <v>46</v>
@@ -13823,10 +13782,10 @@
         <v>66</v>
       </c>
       <c r="I421" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K421" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q421" s="5"/>
     </row>
@@ -13835,7 +13794,7 @@
         <v>43</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C422" s="2">
         <v>39</v>
@@ -13856,10 +13815,10 @@
         <v>75</v>
       </c>
       <c r="I422" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K422" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q422" s="5"/>
     </row>
@@ -13868,7 +13827,7 @@
         <v>44</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C423" s="2">
         <v>94</v>
@@ -13889,10 +13848,10 @@
         <v>66</v>
       </c>
       <c r="I423" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K423" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q423" s="5"/>
     </row>
@@ -13901,7 +13860,7 @@
         <v>45</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C424" s="2">
         <v>73</v>
@@ -13922,10 +13881,10 @@
         <v>69</v>
       </c>
       <c r="I424" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K424" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q424" s="5"/>
     </row>
@@ -13934,7 +13893,7 @@
         <v>46</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C425" s="2">
         <v>79</v>
@@ -13955,10 +13914,10 @@
         <v>67</v>
       </c>
       <c r="I425" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K425" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q425" s="5"/>
     </row>
@@ -13967,7 +13926,7 @@
         <v>47</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C426" s="2">
         <v>87</v>
@@ -13988,10 +13947,10 @@
         <v>74</v>
       </c>
       <c r="I426" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K426" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q426" s="5"/>
     </row>
@@ -14000,7 +13959,7 @@
         <v>48</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C427" s="2">
         <v>45</v>
@@ -14021,10 +13980,10 @@
         <v>60</v>
       </c>
       <c r="I427" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K427" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q427" s="5"/>
     </row>
@@ -14033,7 +13992,7 @@
         <v>49</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C428" s="2">
         <v>28</v>
@@ -14054,10 +14013,10 @@
         <v>45</v>
       </c>
       <c r="I428" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K428" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q428" s="5"/>
     </row>
@@ -14066,7 +14025,7 @@
         <v>50</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C429" s="2">
         <v>36</v>
@@ -14087,7 +14046,7 @@
         <v>50</v>
       </c>
       <c r="I429" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q429" s="5"/>
     </row>
@@ -14096,7 +14055,7 @@
         <v>51</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C430" s="2">
         <v>27</v>
@@ -14117,7 +14076,7 @@
         <v>71</v>
       </c>
       <c r="I430" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q430" s="5"/>
     </row>
@@ -14126,7 +14085,7 @@
         <v>52</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C431" s="2">
         <v>26</v>
@@ -14147,10 +14106,10 @@
         <v>53</v>
       </c>
       <c r="I431" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K431" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q431" s="5"/>
     </row>
@@ -14159,7 +14118,7 @@
         <v>53</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C432" s="2">
         <v>26</v>
@@ -14180,10 +14139,10 @@
         <v>53</v>
       </c>
       <c r="I432" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K432" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q432" s="5"/>
     </row>
@@ -14192,7 +14151,7 @@
         <v>54</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C433" s="2">
         <v>56</v>
@@ -14213,10 +14172,10 @@
         <v>66</v>
       </c>
       <c r="I433" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K433" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q433" s="5"/>
     </row>
@@ -14225,7 +14184,7 @@
         <v>55</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C434" s="2">
         <v>42</v>
@@ -14246,10 +14205,10 @@
         <v>59</v>
       </c>
       <c r="I434" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K434" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q434" s="5"/>
     </row>
@@ -14258,7 +14217,7 @@
         <v>56</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C435" s="2">
         <v>95</v>
@@ -14279,10 +14238,10 @@
         <v>62</v>
       </c>
       <c r="I435" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K435" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q435" s="5"/>
     </row>
@@ -14291,7 +14250,7 @@
         <v>57</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C436" s="2">
         <v>32</v>
@@ -14312,10 +14271,10 @@
         <v>46</v>
       </c>
       <c r="I436" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K436" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q436" s="5"/>
     </row>
@@ -14345,13 +14304,13 @@
         <v>86</v>
       </c>
       <c r="I437" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J437" s="2">
         <v>3</v>
       </c>
       <c r="K437" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q437" s="5"/>
     </row>
@@ -14381,10 +14340,10 @@
         <v>115</v>
       </c>
       <c r="I438" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K438" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q438" s="5"/>
     </row>
@@ -14414,13 +14373,13 @@
         <v>81</v>
       </c>
       <c r="I439" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J439" s="2">
         <v>1</v>
       </c>
       <c r="K439" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q439" s="5"/>
     </row>
@@ -14450,10 +14409,10 @@
         <v>73</v>
       </c>
       <c r="I440" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K440" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q440" s="5"/>
     </row>
@@ -14483,10 +14442,10 @@
         <v>115</v>
       </c>
       <c r="I441" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K441" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q441" s="5"/>
     </row>
@@ -14512,16 +14471,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>81</v>
@@ -14542,7 +14501,7 @@
         <v>80</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -17568,866 +17527,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" style="2"/>
-    <col min="2" max="2" width="20.1640625" style="2" customWidth="1"/>
-    <col min="3" max="12" width="8.83203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="15">
-        <v>46.2</v>
-      </c>
-      <c r="D2" s="15">
-        <v>33.75</v>
-      </c>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="15">
-        <v>65.12</v>
-      </c>
-      <c r="D3" s="15">
-        <v>38.82</v>
-      </c>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="15">
-        <v>30.05</v>
-      </c>
-      <c r="D4" s="15">
-        <v>33.409999999999997</v>
-      </c>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="15">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="15">
-        <v>49.4</v>
-      </c>
-      <c r="D6" s="15">
-        <v>36.64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="15">
-        <v>66.010000000000005</v>
-      </c>
-      <c r="D7" s="15">
-        <v>26.25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="15">
-        <v>91.29</v>
-      </c>
-      <c r="D8" s="15">
-        <v>80.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="15">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="15">
-        <v>45.95</v>
-      </c>
-      <c r="D10" s="15">
-        <v>57.18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C11" s="15">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="15">
-        <v>39.31</v>
-      </c>
-      <c r="D12" s="15">
-        <v>37.01</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="15">
-        <v>0</v>
-      </c>
-      <c r="D13" s="15">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="15">
-        <v>44.41</v>
-      </c>
-      <c r="D14" s="15">
-        <v>31.51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="15">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="15">
-        <v>62.82</v>
-      </c>
-      <c r="D16" s="15">
-        <v>42.29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="15">
-        <v>0</v>
-      </c>
-      <c r="D17" s="15">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="15">
-        <v>28.64</v>
-      </c>
-      <c r="D18" s="15">
-        <v>21.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="15">
-        <v>0</v>
-      </c>
-      <c r="D19" s="15">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="15">
-        <v>52.84</v>
-      </c>
-      <c r="D20" s="15">
-        <v>48.03</v>
-      </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="15">
-        <v>0</v>
-      </c>
-      <c r="D21" s="15">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="15">
-        <v>26.62</v>
-      </c>
-      <c r="D22" s="15">
-        <v>10.54</v>
-      </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="15">
-        <v>69.13</v>
-      </c>
-      <c r="D23" s="15">
-        <v>67.25</v>
-      </c>
-      <c r="E23" s="20"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="15">
-        <v>33.68</v>
-      </c>
-      <c r="D25" s="15">
-        <v>25.64</v>
-      </c>
-      <c r="E25" s="20"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="15">
-        <v>28.4</v>
-      </c>
-      <c r="D26" s="15">
-        <v>16.309999999999999</v>
-      </c>
-      <c r="E26" s="20"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="15">
-        <v>32.409999999999997</v>
-      </c>
-      <c r="D27" s="15">
-        <v>17.78</v>
-      </c>
-      <c r="E27" s="20"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="15">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="D28" s="15">
-        <v>17.79</v>
-      </c>
-      <c r="E28" s="20"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="15">
-        <v>33.97</v>
-      </c>
-      <c r="D29" s="15">
-        <v>16.54</v>
-      </c>
-      <c r="E29" s="20"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="15">
-        <v>24.7</v>
-      </c>
-      <c r="D30" s="15">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="E30" s="20"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="15">
-        <v>32.42</v>
-      </c>
-      <c r="D31" s="15">
-        <v>15.81</v>
-      </c>
-      <c r="E31" s="20"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" s="15">
-        <v>39.950000000000003</v>
-      </c>
-      <c r="D32" s="15">
-        <v>36.53</v>
-      </c>
-      <c r="E32" s="20"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="15">
-        <v>41.82</v>
-      </c>
-      <c r="D33" s="15">
-        <v>67.23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C34" s="15">
-        <v>3.18</v>
-      </c>
-      <c r="D34" s="15">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C35" s="15">
-        <v>24.03</v>
-      </c>
-      <c r="D35" s="15">
-        <v>36.79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="15">
-        <v>56.61</v>
-      </c>
-      <c r="D36" s="15">
-        <v>74.03</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="15">
-        <v>37.159999999999997</v>
-      </c>
-      <c r="D37" s="15">
-        <v>34.85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C38" s="15">
-        <v>49.08</v>
-      </c>
-      <c r="D38" s="15">
-        <v>53.76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C39" s="15">
-        <v>65.569999999999993</v>
-      </c>
-      <c r="D39" s="15">
-        <v>47.27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="15">
-        <v>46.09</v>
-      </c>
-      <c r="D40" s="15">
-        <v>51.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="15">
-        <v>66.81</v>
-      </c>
-      <c r="D41" s="15">
-        <v>68.56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" s="15">
-        <v>33.21</v>
-      </c>
-      <c r="D42" s="15">
-        <v>28.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C43" s="15">
-        <v>41.75</v>
-      </c>
-      <c r="D43" s="15">
-        <v>33.880000000000003</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="15">
-        <v>23.97</v>
-      </c>
-      <c r="D44" s="15">
-        <v>24.96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45" s="15">
-        <v>16.82</v>
-      </c>
-      <c r="D45" s="15">
-        <v>22.47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="15">
-        <v>67.98</v>
-      </c>
-      <c r="D46" s="15">
-        <v>54.06</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C47" s="15">
-        <v>5.42</v>
-      </c>
-      <c r="D47" s="15">
-        <v>12.46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C48" s="15">
-        <v>33.479999999999997</v>
-      </c>
-      <c r="D48" s="15">
-        <v>33.520000000000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" s="15">
-        <v>29.4</v>
-      </c>
-      <c r="D49" s="15">
-        <v>32.92</v>
-      </c>
-      <c r="E49" s="20"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" s="15">
-        <v>42.68</v>
-      </c>
-      <c r="D50" s="15">
-        <v>41.13</v>
-      </c>
-      <c r="E50" s="20"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C51" s="15">
-        <v>14.96</v>
-      </c>
-      <c r="D51" s="15">
-        <v>23.17</v>
-      </c>
-      <c r="E51" s="20"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="15">
-        <v>21.95</v>
-      </c>
-      <c r="D52" s="15">
-        <v>32.340000000000003</v>
-      </c>
-      <c r="E52" s="20"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="15">
-        <v>4.32</v>
-      </c>
-      <c r="D53" s="15">
-        <v>0.99</v>
-      </c>
-      <c r="E53" s="20"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" s="15">
-        <v>25.86</v>
-      </c>
-      <c r="D54" s="15">
-        <v>24.5</v>
-      </c>
-      <c r="E54" s="20"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="15">
-        <v>17.47</v>
-      </c>
-      <c r="D55" s="15">
-        <v>21.61</v>
-      </c>
-      <c r="E55" s="20"/>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="B1:B56" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -18441,16 +17540,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -18458,9 +17557,9 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>111</v>
       </c>
       <c r="D2" s="6">
@@ -18472,9 +17571,9 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>111</v>
       </c>
       <c r="D3" s="6">
@@ -18486,9 +17585,9 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D4" s="6">
@@ -18500,9 +17599,9 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D5" s="6">
@@ -18514,9 +17613,9 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D6" s="6">
@@ -18528,16 +17627,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D7" s="6">
         <v>0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -18545,9 +17644,9 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D8" s="6">
@@ -18559,9 +17658,9 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D9" s="6">
@@ -18573,9 +17672,9 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D10" s="6">
@@ -18587,9 +17686,9 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C11" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D11" s="6">
@@ -18601,9 +17700,9 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D12" s="6">
@@ -18615,9 +17714,9 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D13" s="6">
@@ -18629,9 +17728,9 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D14" s="6">
@@ -18643,16 +17742,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D15" s="6">
         <v>0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -18660,9 +17759,9 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D16" s="6">
@@ -18674,9 +17773,9 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D17" s="6">
@@ -18688,9 +17787,9 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D18" s="6">
@@ -18702,9 +17801,9 @@
         <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D19" s="6">
@@ -18716,9 +17815,9 @@
         <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D20" s="6">
@@ -18730,9 +17829,9 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D21" s="6">
@@ -18746,7 +17845,7 @@
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D22" s="6">
@@ -18760,7 +17859,7 @@
       <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D23" s="6">
@@ -18774,7 +17873,7 @@
       <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D24" s="6">
@@ -18788,7 +17887,7 @@
       <c r="B25" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D25" s="6">
@@ -18802,7 +17901,7 @@
       <c r="B26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="6">
@@ -18816,7 +17915,7 @@
       <c r="B27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D27" s="6">
@@ -18830,7 +17929,7 @@
       <c r="B28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D28" s="6">
@@ -18844,7 +17943,7 @@
       <c r="B29" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D29" s="6">
@@ -18858,7 +17957,7 @@
       <c r="B30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D30" s="6">
@@ -18872,7 +17971,7 @@
       <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D31" s="6">
@@ -18884,9 +17983,9 @@
         <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D32" s="6">
@@ -18898,9 +17997,9 @@
         <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D33" s="6">
@@ -18912,9 +18011,9 @@
         <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C34" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D34" s="6">
@@ -18926,9 +18025,9 @@
         <v>41</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C35" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D35" s="6">
@@ -18940,9 +18039,9 @@
         <v>42</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D36" s="6">
@@ -18954,9 +18053,9 @@
         <v>43</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D37" s="6">
@@ -18968,9 +18067,9 @@
         <v>44</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C38" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D38" s="6">
@@ -18982,9 +18081,9 @@
         <v>45</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C39" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D39" s="6">
@@ -18996,9 +18095,9 @@
         <v>46</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D40" s="6">
@@ -19010,9 +18109,9 @@
         <v>47</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D41" s="6">
@@ -19024,9 +18123,9 @@
         <v>48</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D42" s="6">
@@ -19038,9 +18137,9 @@
         <v>49</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C43" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D43" s="6">
@@ -19052,9 +18151,9 @@
         <v>50</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D44" s="6">
@@ -19066,9 +18165,9 @@
         <v>51</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D45" s="6">
@@ -19080,9 +18179,9 @@
         <v>52</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D46" s="6">
@@ -19094,9 +18193,9 @@
         <v>53</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C47" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D47" s="6">
@@ -19108,9 +18207,9 @@
         <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C48" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D48" s="6">
@@ -19122,9 +18221,9 @@
         <v>55</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D49" s="6">
@@ -19136,9 +18235,9 @@
         <v>56</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D50" s="6">
@@ -19150,9 +18249,9 @@
         <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C51" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D51" s="6">
@@ -19166,7 +18265,7 @@
       <c r="B52" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="19" t="s">
+      <c r="C52" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D52" s="6">
@@ -19180,7 +18279,7 @@
       <c r="B53" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="C53" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D53" s="6">
@@ -19194,7 +18293,7 @@
       <c r="B54" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D54" s="6">
@@ -19208,7 +18307,7 @@
       <c r="B55" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D55" s="6">
@@ -19222,7 +18321,7 @@
       <c r="B56" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D56" s="6">
@@ -19234,10 +18333,10 @@
         <v>3</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>120</v>
+        <v>137</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="D57" s="6">
         <v>24</v>
@@ -19248,10 +18347,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>120</v>
+        <v>138</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="D58" s="6">
         <v>11</v>
@@ -19262,10 +18361,10 @@
         <v>5</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D59" s="6">
         <v>17</v>
@@ -19276,16 +18375,16 @@
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D60" s="6">
         <v>0</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -19293,10 +18392,10 @@
         <v>7</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D61" s="6">
         <v>18</v>
@@ -19307,16 +18406,16 @@
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D62" s="6">
         <v>0</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -19324,10 +18423,10 @@
         <v>9</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D63" s="6">
         <v>25</v>
@@ -19338,16 +18437,16 @@
         <v>10</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D64" s="6">
         <v>0</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -19355,10 +18454,10 @@
         <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D65" s="6">
         <v>14</v>
@@ -19369,16 +18468,16 @@
         <v>12</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D66" s="6">
         <v>0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -19386,10 +18485,10 @@
         <v>13</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D67" s="6">
         <v>14</v>
@@ -19400,16 +18499,16 @@
         <v>14</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D68" s="6">
         <v>0</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -19417,10 +18516,10 @@
         <v>15</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D69" s="6">
         <v>23</v>
@@ -19431,16 +18530,16 @@
         <v>16</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D70" s="6">
         <v>0</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -19448,10 +18547,10 @@
         <v>17</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D71" s="6">
         <v>13</v>
@@ -19462,16 +18561,16 @@
         <v>18</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D72" s="6">
         <v>0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -19479,10 +18578,10 @@
         <v>19</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D73" s="6">
         <v>7</v>
@@ -19493,16 +18592,16 @@
         <v>20</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D74" s="6">
         <v>0</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -19510,16 +18609,16 @@
         <v>21</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -19527,16 +18626,16 @@
         <v>22</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D76" s="6">
         <v>0</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -19546,8 +18645,8 @@
       <c r="B77" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C77" s="19" t="s">
-        <v>119</v>
+      <c r="C77" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D77" s="6">
         <v>1</v>
@@ -19560,8 +18659,8 @@
       <c r="B78" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C78" s="19" t="s">
-        <v>119</v>
+      <c r="C78" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D78" s="6">
         <v>2</v>
@@ -19574,8 +18673,8 @@
       <c r="B79" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C79" s="19" t="s">
-        <v>119</v>
+      <c r="C79" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D79" s="6">
         <v>1</v>
@@ -19588,8 +18687,8 @@
       <c r="B80" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C80" s="19" t="s">
-        <v>119</v>
+      <c r="C80" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D80" s="6">
         <v>3</v>
@@ -19602,8 +18701,8 @@
       <c r="B81" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C81" s="19" t="s">
-        <v>119</v>
+      <c r="C81" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D81" s="6">
         <v>0</v>
@@ -19616,8 +18715,8 @@
       <c r="B82" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C82" s="19" t="s">
-        <v>119</v>
+      <c r="C82" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D82" s="6">
         <v>0</v>
@@ -19630,8 +18729,8 @@
       <c r="B83" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C83" s="19" t="s">
-        <v>119</v>
+      <c r="C83" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D83" s="6">
         <v>0</v>
@@ -19644,8 +18743,8 @@
       <c r="B84" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C84" s="19" t="s">
-        <v>119</v>
+      <c r="C84" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D84" s="6">
         <v>13</v>
@@ -19658,8 +18757,8 @@
       <c r="B85" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C85" s="19" t="s">
-        <v>119</v>
+      <c r="C85" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D85" s="6">
         <v>0</v>
@@ -19672,8 +18771,8 @@
       <c r="B86" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C86" s="19" t="s">
-        <v>119</v>
+      <c r="C86" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D86" s="6">
         <v>0</v>
@@ -19684,10 +18783,10 @@
         <v>38</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D87" s="6">
         <v>0</v>
@@ -19698,10 +18797,10 @@
         <v>39</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D88" s="6">
         <v>0</v>
@@ -19712,10 +18811,10 @@
         <v>40</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D89" s="6">
         <v>0</v>
@@ -19726,10 +18825,10 @@
         <v>41</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D90" s="6">
         <v>2</v>
@@ -19740,10 +18839,10 @@
         <v>42</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D91" s="6">
         <v>1</v>
@@ -19754,10 +18853,10 @@
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C92" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D92" s="6">
         <v>1</v>
@@ -19768,10 +18867,10 @@
         <v>44</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C93" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D93" s="6">
         <v>1</v>
@@ -19782,10 +18881,10 @@
         <v>45</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D94" s="6">
         <v>6</v>
@@ -19796,10 +18895,10 @@
         <v>46</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D95" s="6">
         <v>4</v>
@@ -19810,10 +18909,10 @@
         <v>47</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D96" s="6">
         <v>5</v>
@@ -19824,10 +18923,10 @@
         <v>48</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C97" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D97" s="6">
         <v>4</v>
@@ -19838,10 +18937,10 @@
         <v>49</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D98" s="6">
         <v>3</v>
@@ -19852,10 +18951,10 @@
         <v>50</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D99" s="6">
         <v>0</v>
@@ -19866,10 +18965,10 @@
         <v>51</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C100" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D100" s="6">
         <v>0</v>
@@ -19880,10 +18979,10 @@
         <v>52</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D101" s="6">
         <v>4</v>
@@ -19894,10 +18993,10 @@
         <v>53</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D102" s="6">
         <v>1</v>
@@ -19908,10 +19007,10 @@
         <v>54</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C103" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D103" s="6">
         <v>1</v>
@@ -19922,10 +19021,10 @@
         <v>55</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D104" s="6">
         <v>1</v>
@@ -19936,10 +19035,10 @@
         <v>56</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D105" s="6">
         <v>9</v>
@@ -19950,10 +19049,10 @@
         <v>57</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D106" s="6">
         <v>1</v>
@@ -19966,8 +19065,8 @@
       <c r="B107" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C107" s="19" t="s">
-        <v>119</v>
+      <c r="C107" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D107" s="6">
         <v>1</v>
@@ -19980,8 +19079,8 @@
       <c r="B108" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C108" s="19" t="s">
-        <v>119</v>
+      <c r="C108" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D108" s="6">
         <v>0</v>
@@ -19994,8 +19093,8 @@
       <c r="B109" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C109" s="19" t="s">
-        <v>119</v>
+      <c r="C109" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D109" s="6">
         <v>2</v>
@@ -20008,8 +19107,8 @@
       <c r="B110" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C110" s="19" t="s">
-        <v>119</v>
+      <c r="C110" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D110" s="6">
         <v>6</v>
@@ -20022,14 +19121,14 @@
       <c r="B111" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C111" s="19" t="s">
-        <v>119</v>
+      <c r="C111" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="D111" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E111" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -20038,7 +19137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D333"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -23223,7 +22322,7 @@
         <v>20</v>
       </c>
       <c r="D277" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -23237,7 +22336,7 @@
         <v>20</v>
       </c>
       <c r="D278" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -23248,7 +22347,7 @@
         <v>59</v>
       </c>
       <c r="D279" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -23259,7 +22358,7 @@
         <v>60</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -23270,7 +22369,7 @@
         <v>59</v>
       </c>
       <c r="D281" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -23281,7 +22380,7 @@
         <v>60</v>
       </c>
       <c r="D282" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -23292,7 +22391,7 @@
         <v>59</v>
       </c>
       <c r="D283" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -23303,7 +22402,7 @@
         <v>60</v>
       </c>
       <c r="D284" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -23317,7 +22416,7 @@
         <v>15.9</v>
       </c>
       <c r="D285" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -23328,7 +22427,7 @@
         <v>60</v>
       </c>
       <c r="D286" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -23342,7 +22441,7 @@
         <v>19.3</v>
       </c>
       <c r="D287" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -23353,29 +22452,29 @@
         <v>60</v>
       </c>
       <c r="D288" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B289" t="s">
         <v>59</v>
       </c>
       <c r="D289" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B290" t="s">
         <v>60</v>
       </c>
       <c r="D290" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -23389,7 +22488,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="D291" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -23400,7 +22499,7 @@
         <v>60</v>
       </c>
       <c r="D292" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -23411,7 +22510,7 @@
         <v>59</v>
       </c>
       <c r="D293" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -23422,7 +22521,7 @@
         <v>60</v>
       </c>
       <c r="D294" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -23433,7 +22532,7 @@
         <v>59</v>
       </c>
       <c r="D295" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -23444,7 +22543,7 @@
         <v>60</v>
       </c>
       <c r="D296" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -23455,7 +22554,7 @@
         <v>59</v>
       </c>
       <c r="D297" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -23466,7 +22565,7 @@
         <v>60</v>
       </c>
       <c r="D298" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -23480,7 +22579,7 @@
         <v>19.899999999999999</v>
       </c>
       <c r="D299" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -23491,7 +22590,7 @@
         <v>61</v>
       </c>
       <c r="D300" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -23505,7 +22604,7 @@
         <v>19.899999999999999</v>
       </c>
       <c r="D301" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -23516,7 +22615,7 @@
         <v>61</v>
       </c>
       <c r="D302" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -23527,7 +22626,7 @@
         <v>61</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -23538,7 +22637,7 @@
         <v>61</v>
       </c>
       <c r="D304" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -23549,7 +22648,7 @@
         <v>61</v>
       </c>
       <c r="D305" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -23560,7 +22659,7 @@
         <v>61</v>
       </c>
       <c r="D306" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -23571,7 +22670,7 @@
         <v>61</v>
       </c>
       <c r="D307" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -23582,7 +22681,7 @@
         <v>61</v>
       </c>
       <c r="D308" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -23593,7 +22692,7 @@
         <v>62</v>
       </c>
       <c r="D309" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -23604,7 +22703,7 @@
         <v>63</v>
       </c>
       <c r="D310" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -23618,7 +22717,7 @@
         <v>19.399999999999999</v>
       </c>
       <c r="D311" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -23632,7 +22731,7 @@
         <v>19.8</v>
       </c>
       <c r="D312" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -23643,7 +22742,7 @@
         <v>62</v>
       </c>
       <c r="D313" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -23654,7 +22753,7 @@
         <v>63</v>
       </c>
       <c r="D314" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -23668,7 +22767,7 @@
         <v>19.8</v>
       </c>
       <c r="D315" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -23682,7 +22781,7 @@
         <v>19.8</v>
       </c>
       <c r="D316" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -23693,7 +22792,7 @@
         <v>62</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -23704,7 +22803,7 @@
         <v>63</v>
       </c>
       <c r="D318" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -23715,7 +22814,7 @@
         <v>62</v>
       </c>
       <c r="D319" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -23726,7 +22825,7 @@
         <v>63</v>
       </c>
       <c r="D320" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -23737,7 +22836,7 @@
         <v>62</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -23748,7 +22847,7 @@
         <v>63</v>
       </c>
       <c r="D322" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -23760,7 +22859,7 @@
       </c>
       <c r="C323" s="13"/>
       <c r="D323" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -23772,7 +22871,7 @@
       </c>
       <c r="C324" s="13"/>
       <c r="D324" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -23783,7 +22882,7 @@
         <v>62</v>
       </c>
       <c r="D325" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -23794,7 +22893,7 @@
         <v>63</v>
       </c>
       <c r="D326" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -23805,7 +22904,7 @@
         <v>62</v>
       </c>
       <c r="D327" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -23816,7 +22915,7 @@
         <v>63</v>
       </c>
       <c r="D328" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -23827,7 +22926,7 @@
         <v>64</v>
       </c>
       <c r="D329" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -23838,7 +22937,7 @@
         <v>64</v>
       </c>
       <c r="D330" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -23849,7 +22948,7 @@
         <v>64</v>
       </c>
       <c r="D331" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -23860,7 +22959,7 @@
         <v>64</v>
       </c>
       <c r="D332" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -23871,7 +22970,7 @@
         <v>64</v>
       </c>
       <c r="D333" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -23880,7 +22979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BAD1E68-FDA3-564F-8599-A040E96DB051}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -23891,24 +22990,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -23919,10 +23018,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -23933,7 +23032,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -23947,10 +23046,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -23961,10 +23060,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -23975,7 +23074,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -23989,10 +23088,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C8">
         <v>80</v>
@@ -24003,10 +23102,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -24017,7 +23116,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s">
         <v>61</v>
@@ -24031,10 +23130,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -24045,10 +23144,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -24059,7 +23158,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s">
         <v>70</v>
@@ -24073,35 +23172,35 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C14">
         <v>10</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B16" t="s">
         <v>61</v>
@@ -24110,40 +23209,40 @@
         <v>100</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s">
         <v>70</v>
@@ -24152,11 +23251,11 @@
         <v>100</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>